--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="2673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="2677">
   <si>
     <t>Property</t>
   </si>
@@ -3648,7 +3648,7 @@
     <t>0897</t>
   </si>
   <si>
-    <t>Drainage Vaccination épidémie Grippe</t>
+    <t>Vaccination épidémie Grippe</t>
   </si>
   <si>
     <t>0898</t>
@@ -5664,7 +5664,7 @@
     <t>1276</t>
   </si>
   <si>
-    <t>Enregistrement polygraphique dans le cadre d'une forte suspicion du Syndrome d'Apnées/Hypopnées Obstructives du Sommeil (SAHOS)</t>
+    <t>Enregistrement polygraphique dans le cadre d'une forte suspicion de Syndrome d'Apnées/Hypopnées Obstructives du Sommeil (SAHOS)</t>
   </si>
   <si>
     <t>1277</t>
@@ -8023,6 +8023,18 @@
   </si>
   <si>
     <t>Prise en charge de nouveau patient en tant que médecin traitant</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>Accompagnement à l'essai de fauteuil roulant</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>Groupe (ou stage) psycho-éducatif de responsabilisation pour prévention de la violence et/ou de sa récidive</t>
   </si>
   <si>
     <t/>
@@ -8293,7 +8305,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1324"/>
+  <dimension ref="A1:B1326"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -18881,15 +18893,31 @@
         <v>2670</v>
       </c>
       <c r="B1323" t="s" s="2">
-        <v>2670</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="s" s="2">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="B1324" t="s" s="2">
-        <v>2672</v>
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="s" s="2">
+        <v>2674</v>
+      </c>
+      <c r="B1325" t="s" s="2">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="s" s="2">
+        <v>2675</v>
+      </c>
+      <c r="B1326" t="s" s="2">
+        <v>2676</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="2705">
   <si>
     <t>Property</t>
   </si>
@@ -7591,6 +7591,90 @@
   </si>
   <si>
     <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie du rachis</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Orthoplastie (appareillage d’orteil)</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Orthonyxie (appareillage d’ongle)</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>Onychoplastie (reconstruction de l’ongle)</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Orthèse plantaire (semelle orthopédique)</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>Bilan diagnostique podologique de la prévention de la chute</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>Rééducation du pied (sous la cheville)</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Contention nocturne</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>Soin de pédicurie</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>Traitement de la verrue plantaire par azote liquide</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
   </si>
   <si>
     <t>1630</t>
@@ -8305,7 +8389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1326"/>
+  <dimension ref="A1:B1340"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -18909,15 +18993,127 @@
         <v>2674</v>
       </c>
       <c r="B1325" t="s" s="2">
-        <v>2674</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="s" s="2">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="B1326" t="s" s="2">
-        <v>2676</v>
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="s" s="2">
+        <v>2678</v>
+      </c>
+      <c r="B1327" t="s" s="2">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="s" s="2">
+        <v>2680</v>
+      </c>
+      <c r="B1328" t="s" s="2">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="s" s="2">
+        <v>2682</v>
+      </c>
+      <c r="B1329" t="s" s="2">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="s" s="2">
+        <v>2684</v>
+      </c>
+      <c r="B1330" t="s" s="2">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="s" s="2">
+        <v>2686</v>
+      </c>
+      <c r="B1331" t="s" s="2">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="s" s="2">
+        <v>2688</v>
+      </c>
+      <c r="B1332" t="s" s="2">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="s" s="2">
+        <v>2690</v>
+      </c>
+      <c r="B1333" t="s" s="2">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="s" s="2">
+        <v>2692</v>
+      </c>
+      <c r="B1334" t="s" s="2">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="s" s="2">
+        <v>2694</v>
+      </c>
+      <c r="B1335" t="s" s="2">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="s" s="2">
+        <v>2696</v>
+      </c>
+      <c r="B1336" t="s" s="2">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="s" s="2">
+        <v>2698</v>
+      </c>
+      <c r="B1337" t="s" s="2">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="s" s="2">
+        <v>2700</v>
+      </c>
+      <c r="B1338" t="s" s="2">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="s" s="2">
+        <v>2702</v>
+      </c>
+      <c r="B1339" t="s" s="2">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="s" s="2">
+        <v>2703</v>
+      </c>
+      <c r="B1340" t="s" s="2">
+        <v>2704</v>
       </c>
     </row>
   </sheetData>
